--- a/participantList-584918811.xlsx
+++ b/participantList-584918811.xlsx
@@ -425,9 +425,7 @@
       <c r="K2" t="str">
         <v>否</v>
       </c>
-      <c r="L2" t="str">
-        <v>113.104.203.129</v>
-      </c>
+      <c r="L2" t="str"/>
       <c r="M2" t="str">
         <v>192.168.11.129</v>
       </c>
@@ -435,7 +433,7 @@
         <v>否</v>
       </c>
       <c r="O2" t="str">
-        <v>深圳(中国大陆)</v>
+        <v>-(-)</v>
       </c>
       <c r="P2" t="str">
         <v>LAN</v>
